--- a/artfynd/A 11923-2025 artfynd.xlsx
+++ b/artfynd/A 11923-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131196540</v>
       </c>
       <c r="B2" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11923-2025 artfynd.xlsx
+++ b/artfynd/A 11923-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131196540</v>
       </c>
       <c r="B2" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11923-2025 artfynd.xlsx
+++ b/artfynd/A 11923-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131196540</v>
       </c>
       <c r="B2" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11923-2025 artfynd.xlsx
+++ b/artfynd/A 11923-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131196540</v>
       </c>
       <c r="B2" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11923-2025 artfynd.xlsx
+++ b/artfynd/A 11923-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131196540</v>
       </c>
       <c r="B2" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
